--- a/M143-Bewertungsraster-Protected.xlsx
+++ b/M143-Bewertungsraster-Protected.xlsx
@@ -5,13 +5,13 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sulej\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\modul-143\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01D23DDC-C5CE-4144-B256-D7BD9DC6375C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24EF895E-56D2-4A02-891D-D2A0EDED749F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="yIW9S1EzqRY/xqJqt1yhh4P19Nhu9iuoXPlB9iaRYAbI0E2nEgAeNPmYtDY2ZVoh+l6s9og8duVvMC6fBLJbRg==" workbookSaltValue="SMO2lw7W5HtWe5SKOezMjA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="5235" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="M143" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>Punktevergabe</t>
   </si>
@@ -285,19 +285,34 @@
     <t>36 P. = Note 6.0</t>
   </si>
   <si>
-    <t>https://github.com/Arlind-tbz/modul-143/blob/main/Selbsteinschaetzung.md#a1-ich-kann-vorhandene-datensicherungssysteme-analysieren-und-unter-ber%C3%BCcksichtigung-von-rahmenbedingungen-vorschriften-und-erhobene-daten-einflussfaktoren-ein-datensicherungskonzept-entwickeln-und-fachgerecht-darstellen</t>
-  </si>
-  <si>
-    <t>https://github.com/Arlind-tbz/modul-143/blob/main/Selbsteinschaetzung.md#a2-ich-kann-anhand-von-aktuellen-technischen-l%C3%B6sungen-ein-optimales-datensicherungsverfahren-ausw%C3%A4hlen-ich-ber%C3%BCcksichtige-bei-der-entwicklung-des-datensicherungskonzepts-anspruchsvolle-einflussfaktoren-und-weiss-wie-diese-bei-der-realisierung-technisch-umgesetzt-werden</t>
-  </si>
-  <si>
-    <t>https://github.com/Arlind-tbz/modul-143/blob/main/Selbsteinschaetzung.md#b1-ich-kann-aufgrund-von-technischen-und-betriebswirtschaftlichen-kriterien-ein-individualisiertes-datensicherungskonzept-erstellen-und-auf-machbarkeit-%C3%BCberpr%C3%Bcfen</t>
-  </si>
-  <si>
-    <t>https://github.com/Arlind-tbz/modul-143/blob/main/Selbsteinschaetzung.md#c1-ich-kann-den-aktuellen-und-l%C3%A4ngerfristigen-speicherbedarf-ermitteln-und-individualisierte-l%C3%B6sungen-ger%C3%A4te-speichermedien-sowie-optimale-datenstandorte-on-prem-cloud-ausarbeiten-und-anbieten</t>
-  </si>
-  <si>
-    <t>https://github.com/Arlind-tbz/modul-143/blob/main/Selbsteinschaetzung.md#d2-ich-kann-eine-bestehenden-sicherung--und-wiederherstellungsprozedur-erstellen-pr%C3%BCfen-automatisieren-und-bei-bedarf-optimieren-oder-anpassen</t>
+    <t>https://github.com/Arlind-tbz/modul-143/blob/main/Selbsteinschaetzung.md#a1</t>
+  </si>
+  <si>
+    <t>https://github.com/Arlind-tbz/modul-143/blob/main/Selbsteinschaetzung.md#a2</t>
+  </si>
+  <si>
+    <t>https://github.com/Arlind-tbz/modul-143/blob/main/Selbsteinschaetzung.md#b1</t>
+  </si>
+  <si>
+    <t>https://github.com/Arlind-tbz/modul-143/blob/main/Selbsteinschaetzung.md#c1</t>
+  </si>
+  <si>
+    <t>https://github.com/Arlind-tbz/modul-143/blob/main/Selbsteinschaetzung.md#d1</t>
+  </si>
+  <si>
+    <t>https://github.com/Arlind-tbz/modul-143/blob/main/Selbsteinschaetzung.md#d3</t>
+  </si>
+  <si>
+    <t>https://github.com/Arlind-tbz/modul-143/blob/main/Selbsteinschaetzung.md#d2</t>
+  </si>
+  <si>
+    <t>https://github.com/Arlind-tbz/modul-143/blob/main/Selbsteinschaetzung.md#e1</t>
+  </si>
+  <si>
+    <t>https://github.com/Arlind-tbz/modul-143/blob/main/Selbsteinschaetzung.md#e2</t>
+  </si>
+  <si>
+    <t>https://github.com/Arlind-tbz/modul-143/blob/main/Selbsteinschaetzung.md#f1</t>
   </si>
 </sst>
 </file>
@@ -1100,24 +1115,24 @@
     <xf numFmtId="49" fontId="19" fillId="35" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="25" fillId="33" borderId="0" xfId="42" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1704,26 +1719,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
@@ -1763,9 +1778,9 @@
         <v>11</v>
       </c>
       <c r="C5" s="9">
-        <v>3</v>
-      </c>
-      <c r="D5" s="35" t="s">
+        <v>2.5</v>
+      </c>
+      <c r="D5" s="30" t="s">
         <v>32</v>
       </c>
       <c r="E5" s="11" t="str">
@@ -1782,7 +1797,7 @@
       <c r="G5" s="26"/>
       <c r="H5" s="19"/>
     </row>
-    <row r="6" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="23" t="s">
         <v>10</v>
       </c>
@@ -1792,7 +1807,7 @@
       <c r="C6" s="9">
         <v>3</v>
       </c>
-      <c r="D6" s="35" t="s">
+      <c r="D6" s="30" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="11" t="str">
@@ -1809,7 +1824,7 @@
       <c r="G6" s="26"/>
       <c r="H6" s="20"/>
     </row>
-    <row r="7" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A7" s="23" t="s">
         <v>13</v>
       </c>
@@ -1819,7 +1834,7 @@
       <c r="C7" s="9">
         <v>3</v>
       </c>
-      <c r="D7" s="35" t="s">
+      <c r="D7" s="30" t="s">
         <v>34</v>
       </c>
       <c r="E7" s="11" t="str">
@@ -1846,7 +1861,7 @@
       <c r="C8" s="9">
         <v>3</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="D8" s="30" t="s">
         <v>35</v>
       </c>
       <c r="E8" s="11" t="str">
@@ -1863,7 +1878,7 @@
       <c r="G8" s="26"/>
       <c r="H8" s="20"/>
     </row>
-    <row r="9" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="23" t="s">
         <v>17</v>
       </c>
@@ -1873,8 +1888,8 @@
       <c r="C9" s="9">
         <v>4</v>
       </c>
-      <c r="D9" s="35" t="s">
-        <v>35</v>
+      <c r="D9" s="30" t="s">
+        <v>36</v>
       </c>
       <c r="E9" s="11" t="str">
         <f>IF(Table1[[#This Row],[Punkte 
@@ -1890,7 +1905,7 @@
       <c r="G9" s="26"/>
       <c r="H9" s="20"/>
     </row>
-    <row r="10" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="23" t="s">
         <v>18</v>
       </c>
@@ -1900,8 +1915,8 @@
       <c r="C10" s="9">
         <v>4</v>
       </c>
-      <c r="D10" s="35" t="s">
-        <v>36</v>
+      <c r="D10" s="30" t="s">
+        <v>38</v>
       </c>
       <c r="E10" s="11" t="str">
         <f>IF(Table1[[#This Row],[Punkte 
@@ -1917,7 +1932,7 @@
       <c r="G10" s="26"/>
       <c r="H10" s="20"/>
     </row>
-    <row r="11" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="23" t="s">
         <v>22</v>
       </c>
@@ -1927,8 +1942,8 @@
       <c r="C11" s="9">
         <v>4</v>
       </c>
-      <c r="D11" s="35" t="s">
-        <v>36</v>
+      <c r="D11" s="30" t="s">
+        <v>37</v>
       </c>
       <c r="E11" s="11" t="str">
         <f>IF(Table1[[#This Row],[Punkte 
@@ -1944,7 +1959,7 @@
       <c r="G11" s="26"/>
       <c r="H11" s="20"/>
     </row>
-    <row r="12" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="23" t="s">
         <v>23</v>
       </c>
@@ -1954,8 +1969,8 @@
       <c r="C12" s="9">
         <v>4</v>
       </c>
-      <c r="D12" s="35" t="s">
-        <v>36</v>
+      <c r="D12" s="30" t="s">
+        <v>39</v>
       </c>
       <c r="E12" s="11" t="str">
         <f>IF(Table1[[#This Row],[Punkte 
@@ -1971,7 +1986,7 @@
       <c r="G12" s="26"/>
       <c r="H12" s="20"/>
     </row>
-    <row r="13" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="23" t="s">
         <v>25</v>
       </c>
@@ -1981,8 +1996,8 @@
       <c r="C13" s="9">
         <v>4</v>
       </c>
-      <c r="D13" s="35" t="s">
-        <v>36</v>
+      <c r="D13" s="30" t="s">
+        <v>40</v>
       </c>
       <c r="E13" s="11" t="str">
         <f>IF(Table1[[#This Row],[Punkte 
@@ -1998,7 +2013,7 @@
       <c r="G13" s="26"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="1:8" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="23" t="s">
         <v>27</v>
       </c>
@@ -2008,8 +2023,8 @@
       <c r="C14" s="9">
         <v>3</v>
       </c>
-      <c r="D14" s="35" t="s">
-        <v>36</v>
+      <c r="D14" s="30" t="s">
+        <v>41</v>
       </c>
       <c r="E14" s="11" t="str">
         <f>IF(Table1[[#This Row],[Punkte 
@@ -2033,7 +2048,7 @@
         <f>SUM(Table1[Punkte
 Selbsteinschätzung
 P: 1-4])</f>
-        <v>35</v>
+        <v>34.5</v>
       </c>
       <c r="D15" s="27"/>
       <c r="E15" s="28"/>
@@ -2048,7 +2063,7 @@
       </c>
       <c r="H15" s="22">
         <f>IF(F15=0,IF(C15&lt;36,ROUND(C15*5/36+1,1),6),IF(F15&lt;36,ROUND(F15*5/36+1,1),6))</f>
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3"/>
@@ -2077,23 +2092,11 @@
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Punkte-Eingabe" error="Bitte geben Sie bei der Selbsteinschätzung nur die Werte von 0 bsi 4 ein." sqref="D5:D14" xr:uid="{8EB6E47A-79A9-46CD-A6E1-FE1625EF770A}"/>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="D6" r:id="rId1" location="a2-ich-kann-anhand-von-aktuellen-technischen-l%C3%B6sungen-ein-optimales-datensicherungsverfahren-ausw%C3%A4hlen-ich-ber%C3%BCcksichtige-bei-der-entwicklung-des-datensicherungskonzepts-anspruchsvolle-einflussfaktoren-und-weiss-wie-diese-bei-der-realisierung-technisch-umgesetzt-werden" display="https://github.com/Arlind-tbz/modul-143/blob/main/Selbsteinschaetzung.md#a2-ich-kann-anhand-von-aktuellen-technischen-l%C3%B6sungen-ein-optimales-datensicherungsverfahren-ausw%C3%A4hlen-ich-ber%C3%BCcksichtige-bei-der-entwicklung-des-datensicherungskonzepts-anspruchsvolle-einflussfaktoren-und-weiss-wie-diese-bei-der-realisierung-technisch-umgesetzt-werden" xr:uid="{5FF7B7C6-E073-4D59-8536-BDD914A39D40}"/>
-    <hyperlink ref="D7" r:id="rId2" location="b1-ich-kann-aufgrund-von-technischen-und-betriebswirtschaftlichen-kriterien-ein-individualisiertes-datensicherungskonzept-erstellen-und-auf-machbarkeit-%C3%BCberpr%C3%Bcfen" xr:uid="{B0DCCA9E-6918-4B2E-AC84-39CB9A8277BC}"/>
-    <hyperlink ref="D8" r:id="rId3" location="c1-ich-kann-den-aktuellen-und-l%C3%A4ngerfristigen-speicherbedarf-ermitteln-und-individualisierte-l%C3%B6sungen-ger%C3%A4te-speichermedien-sowie-optimale-datenstandorte-on-prem-cloud-ausarbeiten-und-anbieten" display="https://github.com/Arlind-tbz/modul-143/blob/main/Selbsteinschaetzung.md#c1-ich-kann-den-aktuellen-und-l%C3%A4ngerfristigen-speicherbedarf-ermitteln-und-individualisierte-l%C3%B6sungen-ger%C3%A4te-speichermedien-sowie-optimale-datenstandorte-on-prem-cloud-ausarbeiten-und-anbieten" xr:uid="{D6134E34-4088-4A11-A324-AEA81B983179}"/>
-    <hyperlink ref="D9" r:id="rId4" location="c1-ich-kann-den-aktuellen-und-l%C3%A4ngerfristigen-speicherbedarf-ermitteln-und-individualisierte-l%C3%B6sungen-ger%C3%A4te-speichermedien-sowie-optimale-datenstandorte-on-prem-cloud-ausarbeiten-und-anbieten" display="https://github.com/Arlind-tbz/modul-143/blob/main/Selbsteinschaetzung.md#c1-ich-kann-den-aktuellen-und-l%C3%A4ngerfristigen-speicherbedarf-ermitteln-und-individualisierte-l%C3%B6sungen-ger%C3%A4te-speichermedien-sowie-optimale-datenstandorte-on-prem-cloud-ausarbeiten-und-anbieten" xr:uid="{E8164C74-836F-40EE-938D-20A73E1063EE}"/>
-    <hyperlink ref="D10" r:id="rId5" location="d2-ich-kann-eine-bestehenden-sicherung--und-wiederherstellungsprozedur-erstellen-pr%C3%BCfen-automatisieren-und-bei-bedarf-optimieren-oder-anpassen" xr:uid="{5B78FA8D-C1C3-4C38-BF47-902A9AD9F282}"/>
-    <hyperlink ref="D11" r:id="rId6" location="d2-ich-kann-eine-bestehenden-sicherung--und-wiederherstellungsprozedur-erstellen-pr%C3%BCfen-automatisieren-und-bei-bedarf-optimieren-oder-anpassen" xr:uid="{D895F002-201D-4276-9826-17339CFDDB56}"/>
-    <hyperlink ref="D12" r:id="rId7" location="d2-ich-kann-eine-bestehenden-sicherung--und-wiederherstellungsprozedur-erstellen-pr%C3%BCfen-automatisieren-und-bei-bedarf-optimieren-oder-anpassen" xr:uid="{37363D58-16E9-416B-BF92-C055153FD01D}"/>
-    <hyperlink ref="D5" r:id="rId8" location="a1-ich-kann-vorhandene-datensicherungssysteme-analysieren-und-unter-ber%C3%BCcksichtigung-von-rahmenbedingungen-vorschriften-und-erhobene-daten-einflussfaktoren-ein-datensicherungskonzept-entwickeln-und-fachgerecht-darstellen" display="https://github.com/Arlind-tbz/modul-143/blob/main/Selbsteinschaetzung.md#a1-ich-kann-vorhandene-datensicherungssysteme-analysieren-und-unter-ber%C3%BCcksichtigung-von-rahmenbedingungen-vorschriften-und-erhobene-daten-einflussfaktoren-ein-datensicherungskonzept-entwickeln-und-fachgerecht-darstellen" xr:uid="{CA95A550-6CDF-481F-B655-B8FEC31F570B}"/>
-    <hyperlink ref="D13" r:id="rId9" location="d2-ich-kann-eine-bestehenden-sicherung--und-wiederherstellungsprozedur-erstellen-pr%C3%BCfen-automatisieren-und-bei-bedarf-optimieren-oder-anpassen" xr:uid="{DC9660C7-62F1-49ED-B1D8-F475C4886E36}"/>
-    <hyperlink ref="D14" r:id="rId10" location="d2-ich-kann-eine-bestehenden-sicherung--und-wiederherstellungsprozedur-erstellen-pr%C3%BCfen-automatisieren-und-bei-bedarf-optimieren-oder-anpassen" xr:uid="{1DBAC2C1-138C-4E9D-99B8-D5B5172B9BFF}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="1200" r:id="rId11"/>
-  <legacyDrawing r:id="rId12"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="1200" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId13"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -2307,15 +2310,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <ReferenceId xmlns="6bb99893-d197-453c-bc62-7c0ddc136909" xsi:nil="true"/>
@@ -2328,6 +2322,15 @@
     </SharedWithUsers>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2350,14 +2353,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5C88061-89EB-4B2A-86EF-F4D06CD28E61}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1975346D-1BEC-478D-8DAF-EEE5E87C2B18}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -2373,4 +2368,12 @@
     <ds:schemaRef ds:uri="548dce30-f055-48ee-af5a-fde3f099c0fc"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5C88061-89EB-4B2A-86EF-F4D06CD28E61}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/M143-Bewertungsraster-Protected.xlsx
+++ b/M143-Bewertungsraster-Protected.xlsx
@@ -5,13 +5,13 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\modul-143\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\modul-143\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24EF895E-56D2-4A02-891D-D2A0EDED749F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A46AF8-24CF-427F-AAFB-BD2826060E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="yIW9S1EzqRY/xqJqt1yhh4P19Nhu9iuoXPlB9iaRYAbI0E2nEgAeNPmYtDY2ZVoh+l6s9og8duVvMC6fBLJbRg==" workbookSaltValue="SMO2lw7W5HtWe5SKOezMjA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="M143" sheetId="1" r:id="rId1"/>
@@ -1778,7 +1778,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="9">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="D5" s="30" t="s">
         <v>32</v>
@@ -1905,7 +1905,7 @@
       <c r="G9" s="26"/>
       <c r="H9" s="20"/>
     </row>
-    <row r="10" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="23" t="s">
         <v>18</v>
       </c>
@@ -2013,7 +2013,7 @@
       <c r="G13" s="26"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="23" t="s">
         <v>27</v>
       </c>
@@ -2048,7 +2048,7 @@
         <f>SUM(Table1[Punkte
 Selbsteinschätzung
 P: 1-4])</f>
-        <v>34.5</v>
+        <v>34.75</v>
       </c>
       <c r="D15" s="27"/>
       <c r="E15" s="28"/>
@@ -2127,6 +2127,30 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <ReferenceId xmlns="6bb99893-d197-453c-bc62-7c0ddc136909" xsi:nil="true"/>
+    <SharedWithUsers xmlns="548dce30-f055-48ee-af5a-fde3f099c0fc">
+      <UserInfo>
+        <DisplayName>Sulejmani Arlind</DisplayName>
+        <AccountId>29</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x01010044372F7FFFFB464CA289A341738690BA" ma:contentTypeVersion="7" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="97a43b636e9aba67d8e2b9b3a9ab88b1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6bb99893-d197-453c-bc62-7c0ddc136909" xmlns:ns3="548dce30-f055-48ee-af5a-fde3f099c0fc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ec26850f3cc93c1097f214b09fd18fe" ns2:_="" ns3:_="">
     <xsd:import namespace="6bb99893-d197-453c-bc62-7c0ddc136909"/>
@@ -2309,45 +2333,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <ReferenceId xmlns="6bb99893-d197-453c-bc62-7c0ddc136909" xsi:nil="true"/>
-    <SharedWithUsers xmlns="548dce30-f055-48ee-af5a-fde3f099c0fc">
-      <UserInfo>
-        <DisplayName>Sulejmani Arlind</DisplayName>
-        <AccountId>29</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8F9602D-5A51-4F22-B83A-7B36774BD01D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5C88061-89EB-4B2A-86EF-F4D06CD28E61}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="6bb99893-d197-453c-bc62-7c0ddc136909"/>
-    <ds:schemaRef ds:uri="548dce30-f055-48ee-af5a-fde3f099c0fc"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2371,9 +2360,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5C88061-89EB-4B2A-86EF-F4D06CD28E61}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8F9602D-5A51-4F22-B83A-7B36774BD01D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="6bb99893-d197-453c-bc62-7c0ddc136909"/>
+    <ds:schemaRef ds:uri="548dce30-f055-48ee-af5a-fde3f099c0fc"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>